--- a/TextGame project/Assets/Resources/Story/10.xlsx
+++ b/TextGame project/Assets/Resources/Story/10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECBACAD-E58A-493F-A11E-146D9852CF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA495FA-B3AE-44BD-9988-480A1E760357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -113,28 +113,16 @@
     <t>千叶</t>
   </si>
   <si>
-    <t>门锁了...</t>
-  </si>
-  <si>
     <t>Qianye</t>
   </si>
   <si>
     <t>林深</t>
   </si>
   <si>
-    <t>小问题。</t>
-  </si>
-  <si>
     <t>Linshen</t>
   </si>
   <si>
     <t>（他从口袋里掏出一个小工具，几下就把锁撬开了）</t>
-  </si>
-  <si>
-    <t>哇，你还会这个？</t>
-  </si>
-  <si>
-    <t>侦探必备技能。</t>
   </si>
   <si>
     <t>appearAt</t>
@@ -148,6 +136,22 @@
   </si>
   <si>
     <t>MiniGame</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（皱眉）门锁了...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（看了看锁）小问题。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（惊讶）哇，你还会这个？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（推开门）侦探必备技能。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -220,7 +224,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -239,6 +243,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -798,7 +805,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -817,40 +824,46 @@
       <c r="E3">
         <v>4</v>
       </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J3" s="1">
         <v>-640.83010000000002</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M3" s="1">
         <v>819.16989999999998</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
       </c>
       <c r="R4">
         <v>4</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
       </c>
       <c r="T4" s="1">
         <v>-640.83010000000002</v>
@@ -861,16 +874,19 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
       </c>
       <c r="R5">
         <v>4</v>
+      </c>
+      <c r="S5">
+        <v>2</v>
       </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
@@ -884,13 +900,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="R6">
         <v>4</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
       </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
@@ -903,14 +922,17 @@
       <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>32</v>
+      <c r="B7" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R7">
         <v>4</v>
+      </c>
+      <c r="S7">
+        <v>2</v>
       </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
@@ -921,16 +943,19 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
       </c>
       <c r="R8">
         <v>4</v>
+      </c>
+      <c r="S8">
+        <v>2</v>
       </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
@@ -941,10 +966,10 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>11</v>

--- a/TextGame project/Assets/Resources/Story/10.xlsx
+++ b/TextGame project/Assets/Resources/Story/10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA495FA-B3AE-44BD-9988-480A1E760357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A76190-B45B-4642-AAEF-474E07D1E67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -825,7 +825,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>31</v>
@@ -863,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" s="1">
         <v>-640.83010000000002</v>
@@ -886,7 +886,7 @@
         <v>4</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
@@ -909,7 +909,7 @@
         <v>4</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
@@ -932,7 +932,7 @@
         <v>4</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
@@ -955,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
